--- a/testdata/EmpMigrationData.xlsx
+++ b/testdata/EmpMigrationData.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="20">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -83,19 +83,10 @@
     <t>S</t>
   </si>
   <si>
-    <t>00025</t>
-  </si>
-  <si>
-    <t>00009</t>
-  </si>
-  <si>
     <t>00001</t>
   </si>
   <si>
     <t>00019</t>
-  </si>
-  <si>
-    <t>00006</t>
   </si>
 </sst>
 </file>
@@ -124,8 +115,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -742,8 +733,7 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -755,7 +745,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -1363,26 +1353,26 @@
       <c r="G2" s="2">
         <v>30</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="6" t="s">
+      <c r="H2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>20</v>
+      <c r="M2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="O2" s="2">
         <v>70000</v>
@@ -1408,26 +1398,26 @@
       <c r="G3" s="2">
         <v>30</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="6" t="s">
+      <c r="H3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>20</v>
+      <c r="M3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="O3" s="2">
         <v>70000</v>
@@ -1453,26 +1443,26 @@
       <c r="G4" s="2">
         <v>30</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="6" t="s">
+      <c r="H4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>20</v>
+      <c r="M4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="O4" s="2">
         <v>70000</v>
@@ -1498,26 +1488,26 @@
       <c r="G5" s="2">
         <v>30</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="6" t="s">
+      <c r="H5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>20</v>
+      <c r="M5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="O5" s="2">
         <v>70000</v>
